--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_002/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_002/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -390,11 +395,6 @@
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Predict junction temperatures and coolant pressure drop for rover compute-module cold plate to support CDR</t>
+          <t>Predict junction temperatures and coolant pressure drop for rover compute-module cold plate to support CDR thermal margin assessment</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer (CHT) model using Ansys Fluent 2023 R2 to predict peak FPGA junction temperatures and coolant-side pressure drop for a cold-plate-cooled compute module on a planetary rover. The context of use is to demonstrate component temperature margin against the 85 C derating limit and identify sensitivity drivers (TIM stack-up, flow rate) for design decisions at CDR. Operating envelope: 0.6–1.0 LPM, 35% PG/water, 20–35 C inlet, 130 W board power.</t>
+          <t>Conjugate heat transfer (CHT) model using Ansys Fluent 2023 R2 with steady RANS/SST to predict peak FPGA case temperatures and coolant pressure drop for an Al6061 cold plate assembly. The model supports CDR by demonstrating component temperature margin against the 85 C derating limit and quantifying sensitivity to TIM stack-up and coolant flow rate. Operating envelope: 0.6–1.0 LPM, 35% PG/water, 20–35 C inlet, 130 W total board power.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1349,9 +1349,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (4123-THM-CP-AN-01, rover_therm/cht_coldplate tag cp_cht_v0.9)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Peak FPGA Temperature Margin Requirement</t>
+          <t>Peak FPGA case temperature margin against 85 C derating limit</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Hot FPGA case temperature must remain below the 85 C component derating limit under worst-case operating conditions, including model uncertainty and test-to-model bias, across the validated flow envelope (0.6–1.0 LPM, 35% PG/water, 20–35 C inlet).</t>
+          <t>All FPGA case temperatures must remain below the 85 C component derating limit under the specified operating envelope (0.6–1.0 LPM, 35% PG/water, 20–35 C inlet, 130 W total board power), accounting for model uncertainty and test-observed bias.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 CHT Model</t>
+          <t>Ansys Fluent 2023 R2 CHT Model — Cold Plate Assembly</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Steady RANS SST conjugate heat transfer model of the cold plate and compute module, 6.4M poly-hexcore cells, temp-dependent 35% PG/water properties from CoolProp, solid properties from vendor datasheets.</t>
+          <t>Steady RANS with SST turbulence closure, full conjugate heat transfer through TIMs, copper spreader, and Al6061 cold plate; fluid properties from CoolProp; solid properties from vendor datasheets; 6.4M cell poly-hexcore mesh with 7 prism layers.</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Cold Plate Bench Correlation Dataset</t>
+          <t>Single-board bench correlation dataset</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Single-board rig measurements at 0.8 LPM, 25 C inlet, 130 W: FPGA case temperatures via type-T thermocouples, IR pattern checks, pressure drop via calibrated Coriolis meter; production cold plate hardware, no model tuning applied.</t>
+          <t>Measured FPGA case temperatures (type-T thermocouples), IR thermal pattern maps, and coolant pressure drop (Coriolis meter) from production cold plate bench rig at 0.8 LPM, 25 C inlet, 130 W; no model tuning applied.</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube UQ Ensemble</t>
+          <t>Latin Hypercube Uncertainty Quantification Dataset</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>200-point Latin hypercube sampling over power (±5%), TIM thickness (±25 µm), coolant viscosity (±7%), and interface pressure (±20%), yielding 95% temperature band of ±3.2 C on the hot FPGA at 0.8 LPM.</t>
+          <t>200-point LHS sampling over power (±5%), TIM thickness (±25 µm), coolant viscosity (±7%), and interface pressure (±20%) to characterize 95% temperature spread band on hot FPGA.</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Bench Correlation — Hot FPGA Case Temperature</t>
+          <t>Bench correlation — peak FPGA case temperature</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1993,27 +1993,27 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Model-predicted hot FPGA case temperature compared to thermocouple measurement on production cold plate rig at 0.8 LPM, 25 C inlet, 130 W board power with no post-hoc tuning.</t>
+          <t>CFD-predicted peak FPGA case temperature compared to thermocouple measurements from production cold plate bench rig at 0.8 LPM, 25 C inlet, 130 W. No model tuning applied.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Type-T thermocouple measurement (81.1 C measured vs. 78.4 C predicted)</t>
+          <t>Type-T thermocouple measurements on production cold plate rig</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Test-to-model bias documented (2.7 C); 95% spread from LHS (±3.2 C)</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>If Yes, describe the method</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>2.7 C high bias (model under-predicts by 3.3%); within 85 C limit including combined bias and spread</t>
+          <t>Model predicted 78.4 C; measured 81.1 C; bias = +2.7 C (model under-predicts by 2.7 C)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2025,7 +2025,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Bench Correlation — Board-Average Temperature</t>
+          <t>Bench correlation — board-average temperature</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Model-predicted board-average temperature compared to thermocouple measurement at the same operating point.</t>
+          <t>CFD-predicted board-average case temperature compared to bench measurements at the same operating point.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Type-T thermocouple measurement (64.3 C measured vs. 62.0 C predicted)</t>
+          <t>Type-T thermocouple measurements (board average)</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>2.3 C bias (3.6% error)</t>
+          <t>Model predicted 62.0 C; measured 64.3 C; bias = +2.3 C</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Bench Correlation — Coolant Pressure Drop</t>
+          <t>Bench correlation — coolant pressure drop</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Model-predicted coolant-side pressure drop compared to Coriolis meter measurement at 0.8 LPM, 25 C inlet.</t>
+          <t>CFD-predicted coolant pressure drop compared to Coriolis meter measurement at 0.8 LPM.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Coriolis meter measurement (19.4 kPa measured vs. 18.6 kPa predicted)</t>
+          <t>Coriolis flow meter pressure measurement</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>0.8 kPa bias (4.1% error)</t>
+          <t>Model predicted 18.6 kPa; measured 19.4 kPa; bias = +0.8 kPa (~4.1%)</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study</t>
+          <t>Mesh convergence study</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three-grid convergence study (3.1M, 6.4M, 12.7M poly-hexcore cells) on peak FPGA case temperature. Richardson extrapolation estimate of residual discretization error ~0.8 C from medium to effectively doubled resolution.</t>
+          <t>Three-level mesh refinement study (3.1M / 6.4M / 12.7M cells) assessing discretization error on peak FPGA case temperature. Richardson extrapolation applied to estimate asymptotic change.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation asymptotic value</t>
+          <t>Richardson extrapolation to grid-independent solution</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / grid convergence analysis</t>
+          <t>Richardson extrapolation</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>1.9 C change medium-to-fine; ~0.8 C extrapolated residual error</t>
+          <t>Coarse-to-medium delta = 3.1 C; medium-to-fine delta = 1.9 C; extrapolated residual change medium-to-asymptotic ~0.8 C</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Code Verification — Analytical Benchmark</t>
+          <t>Code verification — analytical and benchmark comparisons</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1D slab conduction patch problem solved with the Fluent model and compared to analytical solution; simplified straight-channel variant Nusselt numbers compared to Gnielinski correlation.</t>
+          <t>1D slab conduction patch problem compared to analytic solution; developing-channel Nusselt numbers in simplified straight-run variant compared to Gnielinski correlation.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Analytical 1D conduction solution; Gnielinski Nusselt number correlation</t>
+          <t>Analytic 1D conduction solution; Gnielinski Nusselt number correlation</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>0.4 C error on conduction patch; 6% error on Nusselt number</t>
+          <t>1D slab: within 0.4 C of analytic; Nusselt: within 6% of Gnielinski</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Simulation software is a commercially released, maintained solver with documented version control and configuration management of project files.</t>
+          <t>Commercial solver with documented QA; version controlled case files in project repository</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 is a commercially released, industry-standard CFD solver with established QA processes. Project files are managed in Git LFS under a tagged release (cp_cht_v0.9) and archived in Windchill (4123-THM-CP-AN-01). Explicit evidence of regression test suites or ISO certification documentation is not cited in the report, but commercial solver practices are well-established.</t>
+          <t>Ansys Fluent 2023 R2 is a commercially released, widely validated CFD solver with vendor-maintained QA processes. Project files are version-controlled in Git LFS under rover_therm/cht_coldplate at tag cp_cht_v0.9, with mesh scripts and case settings stored alongside. The solved case and report are formally archived in Windchill (4123-THM-CP-AN-01). No explicit reference to ISO certification or internal regression suite, but commercial-solver-level QA is implied.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code correctly solves governing equations as demonstrated by benchmark comparisons to analytical or well-established solutions.</t>
+          <t>Code correctness demonstrated against analytic solutions and established correlations</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Two verification benchmarks are documented: (1) 1D slab conduction patch problem matched analytic solution within 0.4 C; (2) developing-channel Nusselt numbers in a straight-run variant were within 6% of the Gnielinski correlation. These provide adequate evidence that Fluent correctly implements conduction and convection physics for this class of problem.</t>
+          <t>Two code-level verification checks are reported: (1) a 1D slab conduction patch problem matched the analytic solution within 0.4 C, verifying the solid conduction solver; (2) developing-channel Nusselt numbers in a simplified straight-run geometry were within 6% of the Gnielinski correlation, verifying the convective heat transfer implementation. These are targeted but meaningful benchmark problems covering the dominant physics modes (conduction and forced convection).</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified residual discretization error acceptable relative to temperature margin requirement.</t>
+          <t>Mesh convergence demonstrated with quantified residual error on the primary QoI</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-grid convergence study performed (3.1M / 6.4M / 12.7M cells, poly-hexcore with seven prism layers, y+ ~0.8). Peak FPGA temperature change was 3.1 C (coarse→medium) and 1.9 C (medium→fine), with Richardson extrapolation estimating ~0.8 C residual error. Medium grid (6.4M) was retained. Grid Convergence Index not formally computed, but trend is monotonically convergent and residual error is small relative to the 85 C limit. Formal GCI or adaptive refinement not documented.</t>
+          <t>Three grids (3.1M / 6.4M / 12.7M cells) were run; peak FPGA case temperature changed 3.1 C (coarse→medium) and 1.9 C (medium→fine). Richardson extrapolation indicates an additional ~0.8 C change from medium to asymptotic. The 6.4M medium grid was retained. Wall resolution y+ ~0.8 is appropriate for SST. Heat balance across the fluid–solid interface was within 0.7%. A formal GCI was not computed, but the monotone convergence and extrapolated residual are documented.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2415,19 +2415,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Iterative solver convergence demonstrated to levels that do not materially affect QoI.</t>
+          <t>Residuals reduced to levels demonstrating iterative convergence</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals reported below 1e-5. Energy balance check across fluid-solid interface matched within 0.7%, confirming global conservation. Both criteria indicate adequate solver convergence for the temperature and pressure drop QoIs.</t>
+          <t>All residuals converged to below 1e-5, which is a tight criterion for steady RANS CHT. Global energy conservation (heat in vs. out across the fluid–solid interface) was verified to within 0.7%, providing an independent convergence quality indicator. No mention of iteration counts or monitoring of QoI convergence history, but the residual target and energy balance together provide adequate evidence.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Model set-up reviewed for correct boundary conditions, geometry fidelity, and load application; independent review documented.</t>
+          <t>Independent review of model setup, boundary conditions, and post-processing</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions are documented (fixed inlet mass flow, zero-gauge outlet pressure, 25 C inlet temperature, component power map applied at package bases). Geometry suppressions are described and justified (fillets &lt;0.2 mm, mounting bosses outside heat path). Heat balance check (0.7%) provides indirect confirmation. However, no evidence of an independent review of model setup by a second analyst is cited in the report. This limits the achieved level.</t>
+          <t>Boundary conditions are clearly documented (inlet mass flow, outlet zero static pressure, 25 C coolant, component power map). Geometry simplifications are explicitly stated (fillets &lt;0.2 mm and off-heat-path bosses suppressed). A sanity check energy balance (0.7% closure) is reported. However, no evidence of an independent peer review or formal model setup checklist is mentioned. The report is signed by a single analyst (J. Ortega) with no co-reviewer credited.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model selection are justified for the flow regime; known model limitations are documented.</t>
+          <t>Governing equations and turbulence model selection justified; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Steady RANS with SST k-omega is appropriate for internal forced convection in the flow regime studied. Full conjugate heat transfer through TIM layers, copper spreader, and aluminum cold plate is modeled. Limitations are explicitly documented: no radiation, no boiling, no manifold surface roughness, no TIM voiding/pump-out, and no purge airflow. Single-phase assumption is justified (no boiling expected). Constitutive fluid properties sourced from CoolProp (temperature-dependent). Solid properties from vendor datasheets.</t>
+          <t>Steady RANS with SST closure is selected and is an appropriate and commonly validated choice for internal cooling passages. Full conjugate heat transfer through TIMs, spreader, and cold plate is included. Single-phase assumption is justified (no boiling expected in the operating envelope). Exclusions (radiation, purge airflow, manifold roughness, TIM voiding) are explicitly documented with forward references for how they will be addressed. Material properties are sourced (CoolProp, vendor datasheets).</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, geometry, and boundary conditions are well-characterized with sources identified; input uncertainties are described.</t>
+          <t>Material properties and boundary conditions from traceable sources; input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Thermal conductivities sourced from vendor datasheets (kCu = 385 W/m-K, kAl = 167 W/m-K, TIM nominal = 3.0 W/m-K). Fluid properties from CoolProp (temperature-dependent). Geometry from latest CAD. Power map specified per component. Input uncertainties for TIM thickness (±25 µm), power (±5%), viscosity (±7%), and interface pressure (±20%) are quantified and used in the LHS study. TIM voiding and pump-out not characterized; lot-to-lot TIM conductivity uncertainty not independently verified.</t>
+          <t>Fluid properties from CoolProp (temperature-dependent), solid conductivities from vendor datasheets (kCu = 385 W/m-K, kAl = 167 W/m-K, TIM nominal = 3.0 W/m-K). Power map applied from component specifications. Coolant inlet conditions set to match bench rig. Input uncertainty ranges are explicitly defined for the LHS study: power ±5%, TIM thickness ±25 µm, coolant viscosity ±7%, interface pressure ±20%. Lot-to-lot viscosity variability is specifically called out. No independent measurement of TIM conductivity on production samples.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2551,19 +2551,19 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is production-representative; sample size and statistical characterization are documented.</t>
+          <t>Test articles are production-representative; sample size documented</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single production cold plate was used in the bench rig. The report does not indicate multiple specimens were tested or that statistical variability across hardware samples was characterized. The single article is described as a production cold plate, which supports representativeness, but one specimen provides no unit-to-unit statistical information. This limits the achieved level.</t>
+          <t>Bench testing used "the production cold plate" — a single production-representative article. No information is given about number of units tested, statistical characterization of the hardware, or sample size justification. A single hardware unit provides limited statistical basis but is consistent with early CDR-phase testing. IR pattern checks were also used to verify spatial uniformity.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test instrumentation is calibrated; measurement uncertainty is characterized; environmental conditions are controlled and reported.</t>
+          <t>Calibrated instrumentation; measurement uncertainty reported; test conditions controlled and documented</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Flow rate measured with a Coriolis meter (high accuracy instrument class). FPGA case temperatures measured with type-T thermocouples; IR used for pattern verification. Inlet temperature and flow rate are specified quantitatively. No explicit calibration records or measurement uncertainty budgets are cited in the report, but Coriolis metering and type-T thermocouples are standard calibrated instruments for this application. Instrumentation selection is appropriate for the QoIs.</t>
+          <t>Coriolis meter used for flow measurement (high-accuracy class), type-T thermocouples at FPGA cases, IR camera for pattern verification. Inlet temperature at 25 C and flow at 0.8 LPM are specified as controlled conditions. Instrument types are identified but explicit calibration records, measurement uncertainty bounds, and environmental control details are not quantified in this report. The instrumentation suite is appropriate for the QoIs and is at a standard level for bench thermal testing.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions are set to match experimental conditions with documented comparison of input parameters.</t>
+          <t>Model inputs match bench test conditions; boundary condition correspondence documented</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>The bench comparison is performed at matched conditions: 0.8 LPM inlet flow, 25 C coolant inlet, 130 W total board power, same 35% PG/water coolant, same production cold plate geometry. No post-hoc tuning was applied. Power distribution in the model (two FPGAs at 35 W, four converters at 8 W) is stated; correspondence to the actual bench power map is asserted but not separately verified by measurement. Matched conditions are adequately documented.</t>
+          <t>The bench operating point (0.8 LPM, 25 C inlet, 130 W total power, 35% PG/water, production cold plate geometry) is explicitly replicated in the model. Inlet mass flow is fixed to match; outlet static pressure is zero; coolant inlet temperature matches test. Power map matches component power dissipation in the test. No model tuning was applied, which preserves the integrity of the comparison. Instrument uncertainty was not formally propagated into the model input uncertainty bands.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to experimental measurements for all primary QoIs; bias and uncertainty documented.</t>
+          <t>Quantitative comparison of model predictions to measurements for all primary QoIs; bias documented</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Three QoIs compared: hot FPGA case temperature (78.4 C predicted vs. 81.1 C measured, 2.7 C bias), board-average temperature (62.0 C vs. 64.3 C, 2.3 C bias), and coolant pressure drop (18.6 kPa vs. 19.4 kPa, 0.8 kPa / 4.1% bias). No model tuning applied. Test-to-model bias is documented and carried forward explicitly into the CDR margin assessment. LHS 95% band (±3.2 C) also quantified. Comparison is at a single operating point (0.8 LPM, 25 C); multi-point comparison across the full 0.6–1.0 LPM envelope is not yet completed.</t>
+          <t>Three QoIs are compared quantitatively: (1) peak FPGA case temperature: 78.4 C predicted vs. 81.1 C measured, bias = +2.7 C; (2) board-average temperature: 62.0 C predicted vs. 64.3 C measured, bias = +2.3 C; (3) coolant pressure drop: 18.6 kPa predicted vs. 19.4 kPa measured, bias = ~4.1%. All comparisons are at a single operating point. Bias direction is consistent (model under-predicts temperature). No statistical uncertainty bands on measurements are reported, and no correlation coefficients or multiple operating points are included in the comparison.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Model outputs directly address the safety/performance decision criterion (85 C derating limit) and are measurable both computationally and experimentally.</t>
+          <t>QoIs directly address the safety and performance decision; measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>The primary QoI (hot FPGA case temperature) directly maps to the 85 C derating limit that governs the CDR acceptance decision. Pressure drop is directly relevant to pump sizing and flow margin. Both QoIs are computed by the model and measured in the bench rig. Sensitivity analysis and UQ results are expressed in the same units as the design limit, enabling direct margin assessment. The connection between QoI and decision is clearly and explicitly established throughout the report.</t>
+          <t>The primary QoI — peak FPGA junction/case temperature — directly maps to the 85 C component derating limit driving the CDR acceptance decision. The secondary QoI (pressure drop) directly relates to pump sizing and margin. Both QoIs are measurable experimentally (thermocouples, Coriolis) and are directly output by the CFD model. The 200-point LHS study further quantifies the 95% spread band (±3.2 C) on the primary QoI, enabling margin assessment with uncertainty. Sensitivity analysis identifies the dominant drivers (TIM thickness, flow rate), providing actionable design guidance.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions span the full COU operating envelope (0.6–1.0 LPM, 20–35 C inlet); validation geometry matches the production assembly.</t>
+          <t>Validation conditions span the intended operating envelope; key physics modes covered</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation was performed at a single operating point (0.8 LPM, 25 C inlet) using a production cold plate. The stated COU envelope is 0.6–1.0 LPM and 20–35 C inlet. The report explicitly acknowledges that the bench matrix should be extended to 0.6 LPM and 35 C inlet to bracket the spec, and that radiation for vacuum-thermal testing is deferred. The single-point validation does not cover the full COU envelope. This gap is documented and a recommendation is made, but it remains unresolved at the time of this assessment.</t>
+          <t>Bench validation was performed at a single operating point (0.8 LPM, 25 C inlet), which falls within but does not span the declared COU envelope (0.6–1.0 LPM, 20–35 C inlet). The report itself explicitly recommends extending the bench matrix to 0.6 LPM and 35 C inlet to bracket the spec, acknowledging this gap. Radiation (relevant for vacuum-thermal testing) is excluded. TIM voiding and pump-out are not modeled. The validation point is the nominal/best-case condition rather than the bounding case. These gaps limit the achieved level despite strong single-point agreement.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CHT model is accepted for its stated COU of supporting CDR by demonstrating FPGA temperature margin against the 85 C derating limit at the nominal operating point (0.8 LPM, 35% PG/water, 25 C inlet, 130 W). Combined worst-case margin (predicted 78.4 C + 2.7 C test bias + 3.2 C UQ spread = 84.3 C) remains below 85 C at the validated operating point. Mesh convergence, solver convergence, analytical benchmarks, and a no-tuning bench correlation across three QoIs are all satisfactory. Acceptance carries the following conditions documented per the analyst's recommendations: (1) TIM assembly process must be locked to 75 µm target with assembly verification; (2) worst-case CDR reviews must carry the combined +2.7 C bias and +3.2 C spread; (3) bench matrix must be extended to 0.6 LPM and 35 C inlet before use outside the validated 0.8 LPM / 25 C operating point; (4) radiation and vacuum-thermal effects must be addressed in the full avionics bay thermal-balance model prior to any use case requiring those physics. Use outside the 0.6–1.0 LPM, 20–35 C, 35% PG/water envelope is not supported by this analysis.</t>
+          <t>The CHT model demonstrates adequate credibility for its CDR support role. Bench correlation at the nominal operating point shows consistent low bias (peak FPGA temperature under-predicted by 2.7 C, pressure drop within 4.1%) with no model tuning. Mesh convergence is documented with Richardson extrapolation indicating ~0.8 C residual discretization error. Code verification against analytic and benchmark solutions is satisfactory. A 200-point LHS quantifies a 95% temperature spread of ±3.2 C. Combining the +2.7 C test bias and +3.2 C spread, the worst-case estimate remains below the 85 C derating limit at 0.8–1.0 LPM, providing a positive CDR finding. Conditions on this acceptance: (1) TIM assembly process must be locked to 75 µm target with verification at assembly; (2) worst-case reviews must carry both the +2.7 C bias and +3.2 C spread; (3) the bench matrix must be extended to 0.6 LPM and 35 C inlet prior to formal thermal-balance closure; (4) radiation effects must be incorporated for vacuum-thermal testing in the next increment. Use outside the 0.6–1.0 LPM / 35% PG/water / 20–35 C inlet envelope is not supported by current validation evidence.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
